--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook" updateLinks="always"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\sango_infinity-main\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320C9D27-864C-4014-88BB-8CD683AAE729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21600" tabRatio="923"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -23,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="313">
   <si>
     <t>序号</t>
   </si>
@@ -991,18 +990,34 @@
   <si>
     <t>关系</t>
   </si>
+  <si>
+    <t>[
+  {
+    "class": "TroopAddSkill",
+    "value": 30
+  }
+]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[
+  {
+    "class": "TroopAddSkill",
+    "value": 29
+  },
+{
+    "class": "TroopAddSkill",
+    "value": 30
+  }
+]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1014,6 +1029,7 @@
       <sz val="11"/>
       <color theme="5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1021,6 +1037,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1028,6 +1045,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1035,12 +1053,14 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1049,6 +1069,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1056,155 +1077,19 @@
       <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1213,222 +1098,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799981688894314"/>
+        <fgColor theme="3" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1438,16 +1137,16 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1455,258 +1154,19 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1744,7 +1204,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1810,67 +1270,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="警告文本" xfId="1" builtinId="11"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="00CCECFF"/>
+      <color rgb="FFCCECFF"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2157,29 +1577,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.75454545454545" style="11" customWidth="1"/>
-    <col min="2" max="2" width="6.25454545454545" style="11" customWidth="1"/>
-    <col min="3" max="3" width="6.75454545454545" style="11" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="11" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="11" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="11" customWidth="1"/>
     <col min="4" max="4" width="70.5" style="11" customWidth="1"/>
-    <col min="5" max="5" width="6.25454545454545" style="11" customWidth="1"/>
-    <col min="6" max="6" width="7.37272727272727" style="11" customWidth="1"/>
-    <col min="7" max="7" width="6.25454545454545" style="11" customWidth="1"/>
-    <col min="8" max="8" width="6.75454545454545" style="11" customWidth="1"/>
-    <col min="9" max="9" width="254.627272727273" style="12" customWidth="1"/>
+    <col min="5" max="5" width="6.25" style="11" customWidth="1"/>
+    <col min="6" max="6" width="7.375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="6.25" style="11" customWidth="1"/>
+    <col min="8" max="8" width="6.75" style="11" customWidth="1"/>
+    <col min="9" max="9" width="254.625" style="12" customWidth="1"/>
     <col min="10" max="10" width="19.5" style="11" customWidth="1"/>
     <col min="11" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="59.25" customHeight="1" spans="1:9">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13"/>
       <c r="B1" s="14" t="s">
         <v>0</v>
@@ -2194,7 +1614,7 @@
       <c r="H1" s="15"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="25.5" customHeight="1" spans="1:9">
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2207,7 +1627,7 @@
       <c r="H2" s="11"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" s="3" customFormat="1" ht="33" customHeight="1" spans="1:9">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,7 +1654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" ht="15.75" customHeight="1" spans="1:9">
+    <row r="4" spans="1:9" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -2263,7 +1683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" s="5" customFormat="1" spans="1:9">
+    <row r="5" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18"/>
       <c r="B5" s="19">
         <v>1</v>
@@ -2290,7 +1710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="21"/>
       <c r="B6" s="22">
         <v>2</v>
@@ -2317,7 +1737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="7"/>
       <c r="B7" s="22">
         <v>3</v>
@@ -2344,7 +1764,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="7"/>
       <c r="B8" s="22">
         <v>4</v>
@@ -2371,7 +1791,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="7"/>
       <c r="B9" s="22">
         <v>5</v>
@@ -2398,7 +1818,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="7"/>
       <c r="B10" s="22">
         <v>6</v>
@@ -2425,7 +1845,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" spans="1:9">
+    <row r="11" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B11" s="23">
         <v>7</v>
       </c>
@@ -2449,7 +1869,7 @@
       </c>
       <c r="I11" s="25"/>
     </row>
-    <row r="12" s="7" customFormat="1" spans="1:9">
+    <row r="12" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B12" s="22">
         <v>8</v>
       </c>
@@ -2475,7 +1895,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" spans="1:9">
+    <row r="13" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="23">
         <v>9</v>
       </c>
@@ -2499,7 +1919,7 @@
       </c>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" s="7" customFormat="1" spans="1:9">
+    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B14" s="22">
         <v>10</v>
       </c>
@@ -2525,7 +1945,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" s="7" customFormat="1" spans="1:9">
+    <row r="15" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B15" s="22">
         <v>11</v>
       </c>
@@ -2551,7 +1971,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="26">
         <v>12</v>
       </c>
@@ -2577,7 +1997,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" s="7" customFormat="1" spans="2:9">
+    <row r="17" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B17" s="22">
         <v>13</v>
       </c>
@@ -2603,7 +2023,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="26">
         <v>14</v>
       </c>
@@ -2629,7 +2049,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="26">
         <v>15</v>
       </c>
@@ -2655,7 +2075,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" s="7" customFormat="1" spans="2:9">
+    <row r="20" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B20" s="22">
         <v>16</v>
       </c>
@@ -2681,7 +2101,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" s="7" customFormat="1" spans="2:9">
+    <row r="21" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B21" s="22">
         <v>17</v>
       </c>
@@ -2707,7 +2127,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" s="7" customFormat="1" spans="2:9">
+    <row r="22" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B22" s="22">
         <v>18</v>
       </c>
@@ -2733,7 +2153,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" ht="42" spans="2:9">
+    <row r="23" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B23" s="26">
         <v>19</v>
       </c>
@@ -2759,7 +2179,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" s="7" customFormat="1" spans="2:9">
+    <row r="24" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B24" s="22">
         <v>20</v>
       </c>
@@ -2785,7 +2205,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="2:9">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B25" s="26">
         <v>21</v>
       </c>
@@ -2808,7 +2228,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="2:9">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B26" s="26">
         <v>22</v>
       </c>
@@ -2834,7 +2254,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" s="7" customFormat="1" spans="2:9">
+    <row r="27" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="22">
         <v>23</v>
       </c>
@@ -2860,7 +2280,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" s="7" customFormat="1" spans="2:9">
+    <row r="28" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B28" s="22">
         <v>24</v>
       </c>
@@ -2886,7 +2306,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" s="7" customFormat="1" spans="2:9">
+    <row r="29" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B29" s="22">
         <v>25</v>
       </c>
@@ -2912,7 +2332,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" s="7" customFormat="1" spans="2:9">
+    <row r="30" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B30" s="22">
         <v>26</v>
       </c>
@@ -2938,7 +2358,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="2:9">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B31" s="26">
         <v>27</v>
       </c>
@@ -2964,7 +2384,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" s="7" customFormat="1" spans="2:9">
+    <row r="32" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B32" s="22">
         <v>28</v>
       </c>
@@ -2990,7 +2410,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" s="7" customFormat="1" spans="2:9">
+    <row r="33" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B33" s="22">
         <v>29</v>
       </c>
@@ -3016,7 +2436,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B34" s="26">
         <v>30</v>
       </c>
@@ -3042,7 +2462,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B35" s="26">
         <v>31</v>
       </c>
@@ -3068,7 +2488,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B36" s="26">
         <v>32</v>
       </c>
@@ -3094,7 +2514,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" s="7" customFormat="1" spans="2:9">
+    <row r="37" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B37" s="22">
         <v>33</v>
       </c>
@@ -3120,7 +2540,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" s="7" customFormat="1" spans="2:9">
+    <row r="38" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B38" s="22">
         <v>34</v>
       </c>
@@ -3146,7 +2566,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" s="8" customFormat="1" ht="12.75" customHeight="1" spans="2:9">
+    <row r="39" spans="2:9" s="8" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="29">
         <v>35</v>
       </c>
@@ -3172,7 +2592,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" s="8" customFormat="1" spans="2:9">
+    <row r="40" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B40" s="29">
         <v>36</v>
       </c>
@@ -3198,7 +2618,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" s="8" customFormat="1" spans="2:9">
+    <row r="41" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B41" s="29">
         <v>37</v>
       </c>
@@ -3224,7 +2644,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" s="8" customFormat="1" spans="2:9">
+    <row r="42" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B42" s="29">
         <v>38</v>
       </c>
@@ -3250,7 +2670,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" s="8" customFormat="1" spans="2:9">
+    <row r="43" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B43" s="29">
         <v>39</v>
       </c>
@@ -3276,7 +2696,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="44" s="8" customFormat="1" spans="2:9">
+    <row r="44" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B44" s="29">
         <v>40</v>
       </c>
@@ -3302,7 +2722,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" s="8" customFormat="1" spans="2:9">
+    <row r="45" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B45" s="29">
         <v>41</v>
       </c>
@@ -3328,7 +2748,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" s="8" customFormat="1" spans="2:9">
+    <row r="46" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B46" s="29">
         <v>42</v>
       </c>
@@ -3354,7 +2774,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" s="8" customFormat="1" spans="2:9">
+    <row r="47" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B47" s="29">
         <v>43</v>
       </c>
@@ -3380,7 +2800,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" s="8" customFormat="1" spans="2:9">
+    <row r="48" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B48" s="29">
         <v>44</v>
       </c>
@@ -3406,7 +2826,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="49" s="8" customFormat="1" spans="2:9">
+    <row r="49" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B49" s="29">
         <v>45</v>
       </c>
@@ -3432,7 +2852,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" s="8" customFormat="1" spans="2:9">
+    <row r="50" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="29">
         <v>46</v>
       </c>
@@ -3458,7 +2878,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" s="8" customFormat="1" spans="2:9">
+    <row r="51" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B51" s="29">
         <v>47</v>
       </c>
@@ -3484,7 +2904,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="52" s="8" customFormat="1" spans="2:9">
+    <row r="52" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B52" s="29">
         <v>48</v>
       </c>
@@ -3510,7 +2930,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" s="8" customFormat="1" spans="2:9">
+    <row r="53" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B53" s="29">
         <v>49</v>
       </c>
@@ -3536,7 +2956,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="54" s="7" customFormat="1" ht="12.75" customHeight="1" spans="2:9">
+    <row r="54" spans="2:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="22">
         <v>50</v>
       </c>
@@ -3562,7 +2982,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="55" s="9" customFormat="1" spans="2:9">
+    <row r="55" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B55" s="23">
         <v>51</v>
       </c>
@@ -3588,7 +3008,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="56" s="9" customFormat="1" spans="2:9">
+    <row r="56" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B56" s="23">
         <v>52</v>
       </c>
@@ -3612,7 +3032,7 @@
       </c>
       <c r="I56" s="33"/>
     </row>
-    <row r="57" spans="2:9">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B57" s="26">
         <v>53</v>
       </c>
@@ -3635,7 +3055,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" s="7" customFormat="1" spans="2:9">
+    <row r="58" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B58" s="22">
         <v>54</v>
       </c>
@@ -3661,7 +3081,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="59" s="7" customFormat="1" spans="2:9">
+    <row r="59" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B59" s="22">
         <v>55</v>
       </c>
@@ -3687,7 +3107,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="60" s="7" customFormat="1" spans="2:9">
+    <row r="60" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B60" s="22">
         <v>56</v>
       </c>
@@ -3713,7 +3133,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="61" s="7" customFormat="1" spans="2:9">
+    <row r="61" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B61" s="22">
         <v>57</v>
       </c>
@@ -3739,7 +3159,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="62" s="7" customFormat="1" spans="2:9">
+    <row r="62" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B62" s="22">
         <v>58</v>
       </c>
@@ -3765,7 +3185,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" s="7" customFormat="1" spans="2:9">
+    <row r="63" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B63" s="22">
         <v>59</v>
       </c>
@@ -3791,7 +3211,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="64" s="7" customFormat="1" spans="2:9">
+    <row r="64" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B64" s="22">
         <v>60</v>
       </c>
@@ -3817,7 +3237,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="65" s="7" customFormat="1" spans="2:10">
+    <row r="65" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B65" s="22">
         <v>61</v>
       </c>
@@ -3843,7 +3263,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="66" s="8" customFormat="1" spans="2:10">
+    <row r="66" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B66" s="29">
         <v>62</v>
       </c>
@@ -3872,7 +3292,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" s="7" customFormat="1" ht="12.75" customHeight="1" spans="2:10">
+    <row r="67" spans="2:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="22">
         <v>63</v>
       </c>
@@ -3898,7 +3318,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="68" s="7" customFormat="1" spans="2:10">
+    <row r="68" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B68" s="22">
         <v>64</v>
       </c>
@@ -3924,7 +3344,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="69" s="7" customFormat="1" spans="2:10">
+    <row r="69" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B69" s="22">
         <v>65</v>
       </c>
@@ -3950,7 +3370,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="70" s="7" customFormat="1" spans="2:10">
+    <row r="70" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B70" s="22">
         <v>66</v>
       </c>
@@ -3976,7 +3396,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="71" s="7" customFormat="1" ht="280" spans="2:10">
+    <row r="71" spans="2:10" s="7" customFormat="1" ht="270" x14ac:dyDescent="0.15">
       <c r="B71" s="22">
         <v>67</v>
       </c>
@@ -4002,7 +3422,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="72" s="7" customFormat="1" spans="2:10">
+    <row r="72" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B72" s="22">
         <v>68</v>
       </c>
@@ -4028,7 +3448,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B73" s="26">
         <v>69</v>
       </c>
@@ -4054,7 +3474,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B74" s="26">
         <v>70</v>
       </c>
@@ -4080,7 +3500,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" ht="81" x14ac:dyDescent="0.15">
       <c r="B75" s="26">
         <v>71</v>
       </c>
@@ -4102,8 +3522,11 @@
       <c r="H75" s="26" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="76" spans="2:10">
+      <c r="I75" s="35" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="135" x14ac:dyDescent="0.15">
       <c r="B76" s="26">
         <v>72</v>
       </c>
@@ -4125,8 +3548,11 @@
       <c r="H76" s="26" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="77" s="7" customFormat="1" spans="2:10">
+      <c r="I76" s="35" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B77" s="22">
         <v>73</v>
       </c>
@@ -4152,7 +3578,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="78" s="7" customFormat="1" spans="2:10">
+    <row r="78" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B78" s="22">
         <v>74</v>
       </c>
@@ -4178,7 +3604,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="79" s="7" customFormat="1" spans="2:10">
+    <row r="79" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B79" s="22">
         <v>75</v>
       </c>
@@ -4204,7 +3630,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" s="8" customFormat="1" spans="2:10">
+    <row r="80" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B80" s="29">
         <v>76</v>
       </c>
@@ -4230,7 +3656,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="81" s="8" customFormat="1" spans="2:9">
+    <row r="81" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B81" s="29">
         <v>77</v>
       </c>
@@ -4256,7 +3682,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="82" s="9" customFormat="1" spans="2:9">
+    <row r="82" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B82" s="23">
         <v>78</v>
       </c>
@@ -4282,7 +3708,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="83" s="9" customFormat="1" spans="2:9">
+    <row r="83" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="23">
         <v>79</v>
       </c>
@@ -4308,7 +3734,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" s="8" customFormat="1" spans="2:9">
+    <row r="84" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="29">
         <v>80</v>
       </c>
@@ -4334,7 +3760,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="85" s="8" customFormat="1" spans="2:9">
+    <row r="85" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B85" s="29">
         <v>81</v>
       </c>
@@ -4360,7 +3786,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="86" s="8" customFormat="1" spans="2:9">
+    <row r="86" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B86" s="29">
         <v>82</v>
       </c>
@@ -4386,7 +3812,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="87" s="8" customFormat="1" spans="2:9">
+    <row r="87" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B87" s="29">
         <v>83</v>
       </c>
@@ -4412,7 +3838,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="88" s="8" customFormat="1" spans="2:9">
+    <row r="88" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B88" s="29">
         <v>84</v>
       </c>
@@ -4438,7 +3864,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="89" s="9" customFormat="1" spans="2:9">
+    <row r="89" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B89" s="23">
         <v>85</v>
       </c>
@@ -4464,7 +3890,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="90" s="9" customFormat="1" spans="2:9">
+    <row r="90" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="23">
         <v>86</v>
       </c>
@@ -4490,7 +3916,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="91" s="9" customFormat="1" spans="2:9">
+    <row r="91" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="23">
         <v>87</v>
       </c>
@@ -4514,7 +3940,7 @@
       </c>
       <c r="I91" s="33"/>
     </row>
-    <row r="92" s="10" customFormat="1" spans="2:9">
+    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B92" s="34">
         <v>88</v>
       </c>
@@ -4540,7 +3966,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="93" s="10" customFormat="1" spans="2:9">
+    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B93" s="34">
         <v>89</v>
       </c>
@@ -4566,7 +3992,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="94" s="9" customFormat="1" spans="2:9">
+    <row r="94" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B94" s="23">
         <v>90</v>
       </c>
@@ -4592,7 +4018,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="95" s="9" customFormat="1" spans="2:9">
+    <row r="95" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B95" s="23">
         <v>91</v>
       </c>
@@ -4618,7 +4044,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="96" s="9" customFormat="1" spans="2:9">
+    <row r="96" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B96" s="23">
         <v>92</v>
       </c>
@@ -4642,7 +4068,7 @@
       </c>
       <c r="I96" s="33"/>
     </row>
-    <row r="97" s="9" customFormat="1" spans="2:9">
+    <row r="97" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B97" s="23">
         <v>93</v>
       </c>
@@ -4666,7 +4092,7 @@
       </c>
       <c r="I97" s="33"/>
     </row>
-    <row r="98" s="9" customFormat="1" spans="2:9">
+    <row r="98" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B98" s="23">
         <v>94</v>
       </c>
@@ -4690,7 +4116,7 @@
       </c>
       <c r="I98" s="33"/>
     </row>
-    <row r="99" s="9" customFormat="1" spans="2:9">
+    <row r="99" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B99" s="23">
         <v>95</v>
       </c>
@@ -4714,7 +4140,7 @@
       </c>
       <c r="I99" s="33"/>
     </row>
-    <row r="100" s="9" customFormat="1" spans="2:9">
+    <row r="100" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B100" s="23">
         <v>96</v>
       </c>
@@ -4738,7 +4164,7 @@
       </c>
       <c r="I100" s="33"/>
     </row>
-    <row r="101" s="9" customFormat="1" spans="2:9">
+    <row r="101" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B101" s="23">
         <v>97</v>
       </c>
@@ -4762,7 +4188,7 @@
       </c>
       <c r="I101" s="33"/>
     </row>
-    <row r="102" s="9" customFormat="1" spans="2:9">
+    <row r="102" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B102" s="23">
         <v>98</v>
       </c>
@@ -4786,7 +4212,7 @@
       </c>
       <c r="I102" s="33"/>
     </row>
-    <row r="103" s="9" customFormat="1" spans="2:9">
+    <row r="103" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B103" s="23">
         <v>99</v>
       </c>
@@ -4810,7 +4236,7 @@
       </c>
       <c r="I103" s="33"/>
     </row>
-    <row r="104" s="9" customFormat="1" spans="2:9">
+    <row r="104" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B104" s="23">
         <v>100</v>
       </c>
@@ -4835,8 +4261,8 @@
       <c r="I104" s="33"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320C9D27-864C-4014-88BB-8CD683AAE729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362EC879-2E69-467C-9DC8-39D7AC49E14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,9 +356,6 @@
     <t>攻击损伤减少20%</t>
   </si>
   <si>
-    <t>[{class:"TroopChangeDamage", value:80, isDefender:1}]</t>
-  </si>
-  <si>
     <t>怒发</t>
   </si>
   <si>
@@ -372,9 +369,6 @@
   </si>
   <si>
     <t>火以外的攻击损伤减半，但火攻的损伤将增为２倍</t>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeDamage", value:50, isDefender:1},{class:"TroopModifyFireDamage",value:200}]</t>
   </si>
   <si>
     <t>强运</t>
@@ -547,9 +541,6 @@
   </si>
   <si>
     <t>于森林使用弩兵战法时伤害增加</t>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeDamage", value:150, isDefender:0,condition:{class:"TerrainCheck",terrainType:6}}]</t>
   </si>
   <si>
     <t>猛者</t>
@@ -1010,6 +1001,18 @@
     "value": 30
   }
 ]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage", value:-20, isDefender:1}]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage", value:-50, isDefender:1},{class:"TroopModifyFireDamage",value:200}]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage", value:50, isDefender:0,condition:{class:"TerrainCheck",terrainType:6}}]</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2459,7 +2462,7 @@
         <v>100</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>107</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.15">
@@ -2467,10 +2470,10 @@
         <v>31</v>
       </c>
       <c r="C35" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="26" t="s">
         <v>108</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>109</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>18</v>
@@ -2485,7 +2488,7 @@
         <v>100</v>
       </c>
       <c r="I35" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.15">
@@ -2493,10 +2496,10 @@
         <v>32</v>
       </c>
       <c r="C36" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" s="26" t="s">
         <v>111</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>112</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>18</v>
@@ -2511,7 +2514,7 @@
         <v>100</v>
       </c>
       <c r="I36" s="20" t="s">
-        <v>113</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -2519,10 +2522,10 @@
         <v>33</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>18</v>
@@ -2537,7 +2540,7 @@
         <v>100</v>
       </c>
       <c r="I37" s="20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -2545,10 +2548,10 @@
         <v>34</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>18</v>
@@ -2563,7 +2566,7 @@
         <v>100</v>
       </c>
       <c r="I38" s="20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="2:9" s="8" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2571,10 +2574,10 @@
         <v>35</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>18</v>
@@ -2589,7 +2592,7 @@
         <v>45</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2597,10 +2600,10 @@
         <v>36</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>18</v>
@@ -2615,7 +2618,7 @@
         <v>45</v>
       </c>
       <c r="I40" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2623,10 +2626,10 @@
         <v>37</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>18</v>
@@ -2641,7 +2644,7 @@
         <v>45</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2649,10 +2652,10 @@
         <v>38</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>18</v>
@@ -2667,7 +2670,7 @@
         <v>45</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2675,10 +2678,10 @@
         <v>39</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>18</v>
@@ -2693,7 +2696,7 @@
         <v>45</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2701,10 +2704,10 @@
         <v>40</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>18</v>
@@ -2719,7 +2722,7 @@
         <v>45</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2727,10 +2730,10 @@
         <v>41</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>18</v>
@@ -2745,7 +2748,7 @@
         <v>45</v>
       </c>
       <c r="I45" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2753,10 +2756,10 @@
         <v>42</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>18</v>
@@ -2771,7 +2774,7 @@
         <v>45</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2779,10 +2782,10 @@
         <v>43</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>18</v>
@@ -2797,7 +2800,7 @@
         <v>45</v>
       </c>
       <c r="I47" s="20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2805,10 +2808,10 @@
         <v>44</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>18</v>
@@ -2823,7 +2826,7 @@
         <v>45</v>
       </c>
       <c r="I48" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2831,10 +2834,10 @@
         <v>45</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>18</v>
@@ -2849,7 +2852,7 @@
         <v>45</v>
       </c>
       <c r="I49" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2857,10 +2860,10 @@
         <v>46</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>18</v>
@@ -2875,7 +2878,7 @@
         <v>45</v>
       </c>
       <c r="I50" s="20" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2883,10 +2886,10 @@
         <v>47</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>18</v>
@@ -2901,7 +2904,7 @@
         <v>45</v>
       </c>
       <c r="I51" s="20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2909,10 +2912,10 @@
         <v>48</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>18</v>
@@ -2927,7 +2930,7 @@
         <v>45</v>
       </c>
       <c r="I52" s="20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -2935,10 +2938,10 @@
         <v>49</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>18</v>
@@ -2953,7 +2956,7 @@
         <v>45</v>
       </c>
       <c r="I53" s="20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54" spans="2:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2961,10 +2964,10 @@
         <v>50</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>18</v>
@@ -2979,7 +2982,7 @@
         <v>45</v>
       </c>
       <c r="I54" s="31" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -2987,10 +2990,10 @@
         <v>51</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>18</v>
@@ -3005,7 +3008,7 @@
         <v>45</v>
       </c>
       <c r="I55" s="20" t="s">
-        <v>170</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -3013,10 +3016,10 @@
         <v>52</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>18</v>
@@ -3037,10 +3040,10 @@
         <v>53</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>18</v>
@@ -3060,10 +3063,10 @@
         <v>54</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D58" s="22" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>18</v>
@@ -3078,7 +3081,7 @@
         <v>67</v>
       </c>
       <c r="I58" s="20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3086,10 +3089,10 @@
         <v>55</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>18</v>
@@ -3104,7 +3107,7 @@
         <v>67</v>
       </c>
       <c r="I59" s="27" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3112,10 +3115,10 @@
         <v>56</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>18</v>
@@ -3130,7 +3133,7 @@
         <v>67</v>
       </c>
       <c r="I60" s="27" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3138,10 +3141,10 @@
         <v>57</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>18</v>
@@ -3156,7 +3159,7 @@
         <v>67</v>
       </c>
       <c r="I61" s="27" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="62" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3164,10 +3167,10 @@
         <v>58</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>18</v>
@@ -3182,7 +3185,7 @@
         <v>67</v>
       </c>
       <c r="I62" s="20" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3190,10 +3193,10 @@
         <v>59</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>18</v>
@@ -3208,7 +3211,7 @@
         <v>67</v>
       </c>
       <c r="I63" s="20" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3216,10 +3219,10 @@
         <v>60</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>18</v>
@@ -3234,7 +3237,7 @@
         <v>67</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3242,10 +3245,10 @@
         <v>61</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>18</v>
@@ -3260,7 +3263,7 @@
         <v>67</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -3268,10 +3271,10 @@
         <v>62</v>
       </c>
       <c r="C66" s="29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>18</v>
@@ -3286,10 +3289,10 @@
         <v>67</v>
       </c>
       <c r="I66" s="20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="67" spans="2:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3297,10 +3300,10 @@
         <v>63</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>18</v>
@@ -3315,7 +3318,7 @@
         <v>67</v>
       </c>
       <c r="I67" s="27" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3323,10 +3326,10 @@
         <v>64</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>18</v>
@@ -3341,7 +3344,7 @@
         <v>67</v>
       </c>
       <c r="I68" s="20" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="69" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3349,10 +3352,10 @@
         <v>65</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>18</v>
@@ -3367,7 +3370,7 @@
         <v>67</v>
       </c>
       <c r="I69" s="20" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3375,10 +3378,10 @@
         <v>66</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>18</v>
@@ -3393,7 +3396,7 @@
         <v>67</v>
       </c>
       <c r="I70" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="2:10" s="7" customFormat="1" ht="270" x14ac:dyDescent="0.15">
@@ -3401,10 +3404,10 @@
         <v>67</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>18</v>
@@ -3419,7 +3422,7 @@
         <v>67</v>
       </c>
       <c r="I71" s="31" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="72" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3427,10 +3430,10 @@
         <v>68</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D72" s="22" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>18</v>
@@ -3445,7 +3448,7 @@
         <v>67</v>
       </c>
       <c r="I72" s="20" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.15">
@@ -3453,10 +3456,10 @@
         <v>69</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>18</v>
@@ -3471,7 +3474,7 @@
         <v>67</v>
       </c>
       <c r="I73" s="27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.15">
@@ -3479,10 +3482,10 @@
         <v>70</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>18</v>
@@ -3497,7 +3500,7 @@
         <v>67</v>
       </c>
       <c r="I74" s="20" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="2:10" ht="81" x14ac:dyDescent="0.15">
@@ -3505,10 +3508,10 @@
         <v>71</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>18</v>
@@ -3523,7 +3526,7 @@
         <v>67</v>
       </c>
       <c r="I75" s="35" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="76" spans="2:10" ht="135" x14ac:dyDescent="0.15">
@@ -3531,10 +3534,10 @@
         <v>72</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>18</v>
@@ -3549,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="I76" s="35" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3557,10 +3560,10 @@
         <v>73</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D77" s="22" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>18</v>
@@ -3572,10 +3575,10 @@
         <v>5</v>
       </c>
       <c r="H77" s="22" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I77" s="20" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="78" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3583,10 +3586,10 @@
         <v>74</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D78" s="22" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>18</v>
@@ -3598,10 +3601,10 @@
         <v>5</v>
       </c>
       <c r="H78" s="22" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I78" s="20" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -3609,10 +3612,10 @@
         <v>75</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D79" s="22" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>18</v>
@@ -3624,10 +3627,10 @@
         <v>5</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I79" s="27" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -3635,10 +3638,10 @@
         <v>76</v>
       </c>
       <c r="C80" s="29" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>18</v>
@@ -3650,10 +3653,10 @@
         <v>5</v>
       </c>
       <c r="H80" s="29" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I80" s="20" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -3661,10 +3664,10 @@
         <v>77</v>
       </c>
       <c r="C81" s="29" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>18</v>
@@ -3676,10 +3679,10 @@
         <v>5</v>
       </c>
       <c r="H81" s="29" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I81" s="20" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -3687,10 +3690,10 @@
         <v>78</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>18</v>
@@ -3702,10 +3705,10 @@
         <v>5</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I82" s="20" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="83" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -3713,10 +3716,10 @@
         <v>79</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>18</v>
@@ -3728,10 +3731,10 @@
         <v>7</v>
       </c>
       <c r="H83" s="23" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I83" s="20" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="84" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -3739,25 +3742,25 @@
         <v>80</v>
       </c>
       <c r="C84" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="D84" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" s="29">
+        <v>2</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="H84" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="D84" s="29" t="s">
+      <c r="I84" s="20" t="s">
         <v>255</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F84" s="29">
-        <v>2</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H84" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="I84" s="20" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="85" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -3765,10 +3768,10 @@
         <v>81</v>
       </c>
       <c r="C85" s="29" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>18</v>
@@ -3777,13 +3780,13 @@
         <v>2</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H85" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I85" s="20" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="86" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -3791,10 +3794,10 @@
         <v>82</v>
       </c>
       <c r="C86" s="29" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>18</v>
@@ -3803,13 +3806,13 @@
         <v>2</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H86" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I86" s="20" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -3817,10 +3820,10 @@
         <v>83</v>
       </c>
       <c r="C87" s="29" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>18</v>
@@ -3829,13 +3832,13 @@
         <v>2</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H87" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I87" s="20" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
@@ -3843,10 +3846,10 @@
         <v>84</v>
       </c>
       <c r="C88" s="29" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>18</v>
@@ -3855,13 +3858,13 @@
         <v>2</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H88" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I88" s="20" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="89" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -3869,10 +3872,10 @@
         <v>85</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>18</v>
@@ -3881,13 +3884,13 @@
         <v>2</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H89" s="23" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I89" s="20" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -3895,10 +3898,10 @@
         <v>86</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>18</v>
@@ -3910,10 +3913,10 @@
         <v>6</v>
       </c>
       <c r="H90" s="23" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I90" s="20" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -3921,10 +3924,10 @@
         <v>87</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>18</v>
@@ -3936,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="H91" s="23" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I91" s="33"/>
     </row>
@@ -3945,10 +3948,10 @@
         <v>88</v>
       </c>
       <c r="C92" s="34" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D92" s="34" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>18</v>
@@ -3960,10 +3963,10 @@
         <v>7</v>
       </c>
       <c r="H92" s="34" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I92" s="20" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -3971,10 +3974,10 @@
         <v>89</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D93" s="34" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>18</v>
@@ -3986,10 +3989,10 @@
         <v>7</v>
       </c>
       <c r="H93" s="34" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I93" s="20" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="94" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -3997,10 +4000,10 @@
         <v>90</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D94" s="23" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>18</v>
@@ -4012,10 +4015,10 @@
         <v>7</v>
       </c>
       <c r="H94" s="23" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I94" s="20" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="95" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -4023,10 +4026,10 @@
         <v>91</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>18</v>
@@ -4038,10 +4041,10 @@
         <v>7</v>
       </c>
       <c r="H95" s="23" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I95" s="20" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="96" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
@@ -4049,10 +4052,10 @@
         <v>92</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D96" s="23" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>18</v>
@@ -4064,7 +4067,7 @@
         <v>8</v>
       </c>
       <c r="H96" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I96" s="33"/>
     </row>
@@ -4073,10 +4076,10 @@
         <v>93</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>18</v>
@@ -4088,7 +4091,7 @@
         <v>8</v>
       </c>
       <c r="H97" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I97" s="33"/>
     </row>
@@ -4097,10 +4100,10 @@
         <v>94</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>18</v>
@@ -4112,7 +4115,7 @@
         <v>8</v>
       </c>
       <c r="H98" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I98" s="33"/>
     </row>
@@ -4121,10 +4124,10 @@
         <v>95</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D99" s="23" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>18</v>
@@ -4136,7 +4139,7 @@
         <v>8</v>
       </c>
       <c r="H99" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I99" s="33"/>
     </row>
@@ -4145,10 +4148,10 @@
         <v>96</v>
       </c>
       <c r="C100" s="23" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>18</v>
@@ -4160,7 +4163,7 @@
         <v>8</v>
       </c>
       <c r="H100" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I100" s="33"/>
     </row>
@@ -4169,10 +4172,10 @@
         <v>97</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>18</v>
@@ -4184,7 +4187,7 @@
         <v>8</v>
       </c>
       <c r="H101" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I101" s="33"/>
     </row>
@@ -4193,10 +4196,10 @@
         <v>98</v>
       </c>
       <c r="C102" s="23" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>18</v>
@@ -4208,7 +4211,7 @@
         <v>8</v>
       </c>
       <c r="H102" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I102" s="33"/>
     </row>
@@ -4217,10 +4220,10 @@
         <v>99</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>18</v>
@@ -4232,7 +4235,7 @@
         <v>8</v>
       </c>
       <c r="H103" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I103" s="33"/>
     </row>
@@ -4241,10 +4244,10 @@
         <v>100</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>18</v>
@@ -4256,7 +4259,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="23" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I104" s="33"/>
     </row>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook" updateLinks="always"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\idea\workspace\xbj268092720\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1FAD7F-F6E5-4377-848B-1FC285BC0EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="923"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -23,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -360,9 +359,6 @@
     <t>攻击损伤减少20%</t>
   </si>
   <si>
-    <t>[{class:"TroopChangeDamage", value:80, isDefender:1}]</t>
-  </si>
-  <si>
     <t>怒发</t>
   </si>
   <si>
@@ -376,9 +372,6 @@
   </si>
   <si>
     <t>火以外的攻击损伤减半，但火攻的损伤将增为２倍</t>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeDamage", value:50, isDefender:1},{class:"TroopModifyFireDamage",value:200}]</t>
   </si>
   <si>
     <t>强运</t>
@@ -551,9 +544,6 @@
   </si>
   <si>
     <t>于森林使用弩兵战法时伤害增加</t>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeDamage", value:150, isDefender:0,condition:{class:"TerrainCheck",terrainType:6}}]</t>
   </si>
   <si>
     <t>猛者</t>
@@ -1020,18 +1010,24 @@
   <si>
     <t>关系</t>
   </si>
+  <si>
+    <t>[{class:"TroopChangeDamage", value:-50, isDefender:1},{class:"TroopModifyFireDamage",value:200}]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage", value:-20, isDefender:1}]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage", value:50, isDefender:0,condition:{class:"TerrainCheck",terrainType:6}}]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1082,144 +1078,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1228,222 +1101,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399945066682943"/>
+        <fgColor theme="6" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799951170384838"/>
+        <fgColor theme="3" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1453,16 +1140,16 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1470,258 +1157,19 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1756,7 +1204,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1822,67 +1270,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="警告文本" xfId="1" builtinId="11"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="00CCECFF"/>
+      <color rgb="FFCCECFF"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1896,7 +1304,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2169,14 +1577,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.75" style="10" customWidth="1"/>
     <col min="2" max="2" width="6.25" style="10" customWidth="1"/>
@@ -2191,7 +1599,7 @@
     <col min="11" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="59.25" customHeight="1" spans="1:9">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12"/>
       <c r="B1" s="13" t="s">
         <v>0</v>
@@ -2206,7 +1614,7 @@
       <c r="H1" s="14"/>
       <c r="I1" s="15"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="25.5" customHeight="1" spans="1:9">
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2219,7 +1627,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="11"/>
     </row>
-    <row r="3" s="3" customFormat="1" ht="33" customHeight="1" spans="1:9">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -2246,7 +1654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" ht="15.75" customHeight="1" spans="1:9">
+    <row r="4" spans="1:9" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,7 +1683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" s="5" customFormat="1" spans="1:9">
+    <row r="5" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="17"/>
       <c r="B5" s="18">
         <v>1</v>
@@ -2302,7 +1710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="20"/>
       <c r="B6" s="21">
         <v>2</v>
@@ -2329,7 +1737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="7"/>
       <c r="B7" s="21">
         <v>3</v>
@@ -2356,7 +1764,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="7"/>
       <c r="B8" s="21">
         <v>4</v>
@@ -2383,7 +1791,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="7"/>
       <c r="B9" s="21">
         <v>5</v>
@@ -2410,7 +1818,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="7"/>
       <c r="B10" s="21">
         <v>6</v>
@@ -2437,7 +1845,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" spans="1:9">
+    <row r="11" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B11" s="22">
         <v>7</v>
       </c>
@@ -2461,7 +1869,7 @@
       </c>
       <c r="I11" s="24"/>
     </row>
-    <row r="12" s="7" customFormat="1" spans="1:9">
+    <row r="12" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B12" s="21">
         <v>8</v>
       </c>
@@ -2487,7 +1895,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" spans="1:9">
+    <row r="13" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="22">
         <v>9</v>
       </c>
@@ -2511,7 +1919,7 @@
       </c>
       <c r="I13" s="24"/>
     </row>
-    <row r="14" s="7" customFormat="1" spans="1:9">
+    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B14" s="21">
         <v>10</v>
       </c>
@@ -2537,7 +1945,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" s="7" customFormat="1" spans="1:9">
+    <row r="15" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B15" s="21">
         <v>11</v>
       </c>
@@ -2563,7 +1971,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="25">
         <v>12</v>
       </c>
@@ -2589,7 +1997,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" s="7" customFormat="1" spans="2:9">
+    <row r="17" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B17" s="21">
         <v>13</v>
       </c>
@@ -2615,7 +2023,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="25">
         <v>14</v>
       </c>
@@ -2641,7 +2049,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="25">
         <v>15</v>
       </c>
@@ -2667,7 +2075,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" s="7" customFormat="1" spans="2:9">
+    <row r="20" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B20" s="21">
         <v>16</v>
       </c>
@@ -2693,7 +2101,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" s="7" customFormat="1" spans="2:9">
+    <row r="21" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B21" s="21">
         <v>17</v>
       </c>
@@ -2719,7 +2127,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" s="7" customFormat="1" spans="2:9">
+    <row r="22" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
         <v>18</v>
       </c>
@@ -2745,7 +2153,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" ht="40.5" spans="2:9">
+    <row r="23" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B23" s="25">
         <v>19</v>
       </c>
@@ -2771,7 +2179,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" s="7" customFormat="1" spans="2:9">
+    <row r="24" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B24" s="21">
         <v>20</v>
       </c>
@@ -2797,7 +2205,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="2:9">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B25" s="25">
         <v>21</v>
       </c>
@@ -2823,7 +2231,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="2:9">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B26" s="25">
         <v>22</v>
       </c>
@@ -2849,7 +2257,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" s="7" customFormat="1" spans="2:9">
+    <row r="27" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="21">
         <v>23</v>
       </c>
@@ -2875,7 +2283,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" s="7" customFormat="1" spans="2:9">
+    <row r="28" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
         <v>24</v>
       </c>
@@ -2901,7 +2309,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" s="7" customFormat="1" spans="2:9">
+    <row r="29" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B29" s="21">
         <v>25</v>
       </c>
@@ -2927,7 +2335,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" s="7" customFormat="1" spans="2:9">
+    <row r="30" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B30" s="21">
         <v>26</v>
       </c>
@@ -2953,7 +2361,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="2:9">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B31" s="25">
         <v>27</v>
       </c>
@@ -2979,7 +2387,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" s="7" customFormat="1" spans="2:9">
+    <row r="32" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B32" s="21">
         <v>28</v>
       </c>
@@ -3005,7 +2413,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" s="7" customFormat="1" spans="2:9">
+    <row r="33" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B33" s="21">
         <v>29</v>
       </c>
@@ -3031,7 +2439,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B34" s="25">
         <v>30</v>
       </c>
@@ -3053,19 +2461,19 @@
       <c r="H34" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="I34" s="19" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9">
+      <c r="I34" s="34" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B35" s="25">
         <v>31</v>
       </c>
       <c r="C35" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="25" t="s">
         <v>109</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>110</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>18</v>
@@ -3080,18 +2488,18 @@
         <v>101</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B36" s="25">
         <v>32</v>
       </c>
       <c r="C36" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="25" t="s">
         <v>112</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>113</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>18</v>
@@ -3105,19 +2513,19 @@
       <c r="H36" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="I36" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="37" s="7" customFormat="1" spans="2:9">
+      <c r="I36" s="34" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B37" s="21">
         <v>33</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>18</v>
@@ -3132,18 +2540,18 @@
         <v>101</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38" s="7" customFormat="1" spans="2:9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B38" s="21">
         <v>34</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>18</v>
@@ -3158,18 +2566,18 @@
         <v>101</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" s="8" customFormat="1" ht="12.75" customHeight="1" spans="2:9">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="8" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="28">
         <v>35</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>18</v>
@@ -3184,18 +2592,18 @@
         <v>45</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="40" s="8" customFormat="1" spans="2:9">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B40" s="28">
         <v>36</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>18</v>
@@ -3210,18 +2618,18 @@
         <v>45</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="41" s="8" customFormat="1" spans="2:9">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B41" s="28">
         <v>37</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>18</v>
@@ -3236,18 +2644,18 @@
         <v>45</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="42" s="8" customFormat="1" spans="2:9">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B42" s="28">
         <v>38</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>18</v>
@@ -3262,18 +2670,18 @@
         <v>45</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43" s="8" customFormat="1" spans="2:9">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B43" s="28">
         <v>39</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>18</v>
@@ -3288,18 +2696,18 @@
         <v>45</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" s="8" customFormat="1" spans="2:9">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B44" s="28">
         <v>40</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>18</v>
@@ -3314,18 +2722,18 @@
         <v>45</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45" s="8" customFormat="1" spans="2:9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B45" s="28">
         <v>41</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>18</v>
@@ -3340,18 +2748,18 @@
         <v>45</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="46" s="8" customFormat="1" spans="2:9">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B46" s="28">
         <v>42</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>18</v>
@@ -3366,18 +2774,18 @@
         <v>45</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47" s="8" customFormat="1" spans="2:9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B47" s="28">
         <v>43</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>18</v>
@@ -3392,18 +2800,18 @@
         <v>45</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="48" s="8" customFormat="1" spans="2:9">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B48" s="28">
         <v>44</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>18</v>
@@ -3418,18 +2826,18 @@
         <v>45</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="49" s="8" customFormat="1" spans="2:9">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B49" s="28">
         <v>45</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>18</v>
@@ -3444,18 +2852,18 @@
         <v>45</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="50" s="8" customFormat="1" spans="2:9">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="28">
         <v>46</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>18</v>
@@ -3470,18 +2878,18 @@
         <v>45</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="51" s="8" customFormat="1" spans="2:9">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B51" s="28">
         <v>47</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>18</v>
@@ -3496,18 +2904,18 @@
         <v>45</v>
       </c>
       <c r="I51" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="52" s="8" customFormat="1" spans="2:9">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B52" s="28">
         <v>48</v>
       </c>
       <c r="C52" s="28" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>18</v>
@@ -3522,18 +2930,18 @@
         <v>45</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53" s="8" customFormat="1" spans="2:9">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B53" s="28">
         <v>49</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>18</v>
@@ -3548,18 +2956,18 @@
         <v>45</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="54" s="7" customFormat="1" ht="12.75" customHeight="1" spans="2:9">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="21">
         <v>50</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>18</v>
@@ -3574,18 +2982,18 @@
         <v>45</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="55" s="6" customFormat="1" spans="2:9">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B55" s="22">
         <v>51</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>18</v>
@@ -3599,19 +3007,19 @@
       <c r="H55" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I55" s="19" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="56" s="6" customFormat="1" spans="2:9">
+      <c r="I55" s="34" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B56" s="22">
         <v>52</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>18</v>
@@ -3627,15 +3035,15 @@
       </c>
       <c r="I56" s="24"/>
     </row>
-    <row r="57" spans="2:9">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B57" s="25">
         <v>53</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>18</v>
@@ -3650,15 +3058,15 @@
         <v>101</v>
       </c>
     </row>
-    <row r="58" s="7" customFormat="1" spans="2:9">
+    <row r="58" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B58" s="21">
         <v>54</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>18</v>
@@ -3673,18 +3081,18 @@
         <v>67</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="59" s="7" customFormat="1" spans="2:9">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B59" s="21">
         <v>55</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>18</v>
@@ -3699,18 +3107,18 @@
         <v>67</v>
       </c>
       <c r="I59" s="26" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="60" s="7" customFormat="1" spans="2:9">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B60" s="21">
         <v>56</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>18</v>
@@ -3725,18 +3133,18 @@
         <v>67</v>
       </c>
       <c r="I60" s="26" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="61" s="7" customFormat="1" spans="2:9">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B61" s="21">
         <v>57</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>18</v>
@@ -3751,18 +3159,18 @@
         <v>67</v>
       </c>
       <c r="I61" s="26" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="62" s="7" customFormat="1" spans="2:9">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B62" s="21">
         <v>58</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>18</v>
@@ -3777,18 +3185,18 @@
         <v>67</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="63" s="7" customFormat="1" spans="2:9">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B63" s="21">
         <v>59</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>18</v>
@@ -3803,18 +3211,18 @@
         <v>67</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="64" s="7" customFormat="1" spans="2:9">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B64" s="21">
         <v>60</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>18</v>
@@ -3829,18 +3237,18 @@
         <v>67</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="65" s="7" customFormat="1" spans="2:10">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B65" s="21">
         <v>61</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>18</v>
@@ -3855,18 +3263,18 @@
         <v>67</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="66" s="8" customFormat="1" spans="2:10">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B66" s="28">
         <v>62</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>18</v>
@@ -3881,21 +3289,21 @@
         <v>67</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="67" s="7" customFormat="1" ht="12.75" customHeight="1" spans="2:10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="21">
         <v>63</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>18</v>
@@ -3910,18 +3318,18 @@
         <v>67</v>
       </c>
       <c r="I67" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="68" s="7" customFormat="1" spans="2:10">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B68" s="21">
         <v>64</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>18</v>
@@ -3936,18 +3344,18 @@
         <v>67</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="69" s="7" customFormat="1" spans="2:10">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B69" s="21">
         <v>65</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>18</v>
@@ -3962,18 +3370,18 @@
         <v>67</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="70" s="7" customFormat="1" spans="2:10">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B70" s="21">
         <v>66</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>18</v>
@@ -3988,18 +3396,18 @@
         <v>67</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="71" s="7" customFormat="1" ht="270" spans="2:10">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" s="7" customFormat="1" ht="270" x14ac:dyDescent="0.15">
       <c r="B71" s="21">
         <v>67</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>18</v>
@@ -4014,18 +3422,18 @@
         <v>67</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="72" s="7" customFormat="1" spans="2:10">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B72" s="21">
         <v>68</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>18</v>
@@ -4040,18 +3448,18 @@
         <v>67</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B73" s="25">
         <v>69</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>18</v>
@@ -4066,18 +3474,18 @@
         <v>67</v>
       </c>
       <c r="I73" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B74" s="25">
         <v>70</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>18</v>
@@ -4092,18 +3500,18 @@
         <v>67</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="75" ht="81" spans="2:10">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="81" x14ac:dyDescent="0.15">
       <c r="B75" s="25">
         <v>71</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>18</v>
@@ -4118,18 +3526,18 @@
         <v>67</v>
       </c>
       <c r="I75" s="32" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="76" ht="135" spans="2:10">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="135" x14ac:dyDescent="0.15">
       <c r="B76" s="25">
         <v>72</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>18</v>
@@ -4144,18 +3552,18 @@
         <v>67</v>
       </c>
       <c r="I76" s="32" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="77" s="7" customFormat="1" spans="2:10">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B77" s="21">
         <v>73</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>18</v>
@@ -4167,21 +3575,21 @@
         <v>5</v>
       </c>
       <c r="H77" s="21" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="78" s="7" customFormat="1" spans="2:10">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B78" s="21">
         <v>74</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>18</v>
@@ -4193,21 +3601,21 @@
         <v>5</v>
       </c>
       <c r="H78" s="21" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="79" s="7" customFormat="1" spans="2:10">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B79" s="21">
         <v>75</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>18</v>
@@ -4219,21 +3627,21 @@
         <v>5</v>
       </c>
       <c r="H79" s="21" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I79" s="26" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="80" s="8" customFormat="1" spans="2:10">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B80" s="28">
         <v>76</v>
       </c>
       <c r="C80" s="28" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>18</v>
@@ -4245,21 +3653,21 @@
         <v>5</v>
       </c>
       <c r="H80" s="28" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="81" s="8" customFormat="1" spans="2:9">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B81" s="28">
         <v>77</v>
       </c>
       <c r="C81" s="28" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>18</v>
@@ -4271,21 +3679,21 @@
         <v>5</v>
       </c>
       <c r="H81" s="28" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="82" s="6" customFormat="1" spans="2:9">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B82" s="22">
         <v>78</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D82" s="22" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>18</v>
@@ -4297,21 +3705,21 @@
         <v>5</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I82" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="83" s="6" customFormat="1" spans="2:9">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="22">
         <v>79</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>18</v>
@@ -4323,47 +3731,47 @@
         <v>7</v>
       </c>
       <c r="H83" s="22" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I83" s="19" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="84" s="8" customFormat="1" spans="2:9">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="28">
         <v>80</v>
       </c>
       <c r="C84" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="D84" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" s="28">
+        <v>2</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="H84" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="D84" s="28" t="s">
+      <c r="I84" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="E84" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F84" s="28">
-        <v>2</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="H84" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="I84" s="19" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="85" s="8" customFormat="1" spans="2:9">
+    </row>
+    <row r="85" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B85" s="28">
         <v>81</v>
       </c>
       <c r="C85" s="28" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>18</v>
@@ -4372,24 +3780,24 @@
         <v>2</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H85" s="28" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="86" s="8" customFormat="1" spans="2:9">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B86" s="28">
         <v>82</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D86" s="28" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>18</v>
@@ -4398,24 +3806,24 @@
         <v>2</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H86" s="28" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="87" s="8" customFormat="1" spans="2:9">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B87" s="28">
         <v>83</v>
       </c>
       <c r="C87" s="28" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>18</v>
@@ -4424,24 +3832,24 @@
         <v>2</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H87" s="28" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I87" s="19" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="88" s="8" customFormat="1" spans="2:9">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B88" s="28">
         <v>84</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>18</v>
@@ -4450,24 +3858,24 @@
         <v>2</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H88" s="28" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I88" s="19" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="89" s="6" customFormat="1" spans="2:9">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B89" s="22">
         <v>85</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D89" s="22" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>18</v>
@@ -4476,24 +3884,24 @@
         <v>2</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H89" s="22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I89" s="19" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="90" s="6" customFormat="1" spans="2:9">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="22">
         <v>86</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D90" s="22" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>18</v>
@@ -4505,21 +3913,21 @@
         <v>6</v>
       </c>
       <c r="H90" s="22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I90" s="19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="91" s="6" customFormat="1" spans="2:9">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="22">
         <v>87</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D91" s="22" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>18</v>
@@ -4531,19 +3939,19 @@
         <v>6</v>
       </c>
       <c r="H91" s="22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I91" s="24"/>
     </row>
-    <row r="92" s="9" customFormat="1" spans="2:9">
+    <row r="92" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B92" s="33">
         <v>88</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D92" s="33" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>18</v>
@@ -4555,21 +3963,21 @@
         <v>7</v>
       </c>
       <c r="H92" s="33" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I92" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="93" s="9" customFormat="1" spans="2:9">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B93" s="33">
         <v>89</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D93" s="33" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>18</v>
@@ -4581,21 +3989,21 @@
         <v>7</v>
       </c>
       <c r="H93" s="33" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I93" s="19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="94" s="6" customFormat="1" spans="2:9">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B94" s="22">
         <v>90</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E94" s="9" t="s">
         <v>18</v>
@@ -4607,21 +4015,21 @@
         <v>7</v>
       </c>
       <c r="H94" s="22" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I94" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="95" s="6" customFormat="1" spans="2:9">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B95" s="22">
         <v>91</v>
       </c>
       <c r="C95" s="22" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D95" s="22" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>18</v>
@@ -4633,21 +4041,21 @@
         <v>7</v>
       </c>
       <c r="H95" s="22" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I95" s="19" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="96" s="6" customFormat="1" spans="2:9">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B96" s="22">
         <v>92</v>
       </c>
       <c r="C96" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D96" s="22" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>18</v>
@@ -4659,19 +4067,19 @@
         <v>8</v>
       </c>
       <c r="H96" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I96" s="24"/>
     </row>
-    <row r="97" s="6" customFormat="1" spans="2:9">
+    <row r="97" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B97" s="22">
         <v>93</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D97" s="22" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>18</v>
@@ -4683,19 +4091,19 @@
         <v>8</v>
       </c>
       <c r="H97" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I97" s="24"/>
     </row>
-    <row r="98" s="6" customFormat="1" spans="2:9">
+    <row r="98" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B98" s="22">
         <v>94</v>
       </c>
       <c r="C98" s="22" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D98" s="22" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>18</v>
@@ -4707,19 +4115,19 @@
         <v>8</v>
       </c>
       <c r="H98" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I98" s="24"/>
     </row>
-    <row r="99" s="6" customFormat="1" spans="2:9">
+    <row r="99" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B99" s="22">
         <v>95</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D99" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>18</v>
@@ -4731,19 +4139,19 @@
         <v>8</v>
       </c>
       <c r="H99" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I99" s="24"/>
     </row>
-    <row r="100" s="6" customFormat="1" spans="2:9">
+    <row r="100" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B100" s="22">
         <v>96</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D100" s="22" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>18</v>
@@ -4755,19 +4163,19 @@
         <v>8</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I100" s="24"/>
     </row>
-    <row r="101" s="6" customFormat="1" spans="2:9">
+    <row r="101" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B101" s="22">
         <v>97</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D101" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>18</v>
@@ -4779,21 +4187,21 @@
         <v>8</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I101" s="24" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="102" s="6" customFormat="1" spans="2:9">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B102" s="22">
         <v>98</v>
       </c>
       <c r="C102" s="22" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D102" s="22" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>18</v>
@@ -4805,19 +4213,19 @@
         <v>8</v>
       </c>
       <c r="H102" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I102" s="24"/>
     </row>
-    <row r="103" s="6" customFormat="1" spans="2:9">
+    <row r="103" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B103" s="22">
         <v>99</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D103" s="22" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>18</v>
@@ -4829,21 +4237,21 @@
         <v>8</v>
       </c>
       <c r="H103" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I103" s="24" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="104" s="6" customFormat="1" spans="2:9">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B104" s="22">
         <v>100</v>
       </c>
       <c r="C104" s="22" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D104" s="22" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>18</v>
@@ -4855,13 +4263,13 @@
         <v>9</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I104" s="24"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="318">
   <si>
     <t>序号</t>
   </si>
@@ -549,13 +549,13 @@
     <t>猛者</t>
   </si>
   <si>
-    <t>以战法让敌方部队移动区格时，可让敌将负伤</t>
+    <t>以战法让敌方部队移动区格时，可让敌将负伤，攻击损伤增加20%</t>
   </si>
   <si>
     <t>护卫</t>
   </si>
   <si>
-    <t>同部队的武将不会战死、负伤</t>
+    <t>同部队的武将不会战死、负伤，攻击损伤减少20%</t>
   </si>
   <si>
     <t>火攻</t>
@@ -1021,6 +1021,12 @@
   <si>
     <t>[{class:"TroopChangeDamage", value:50, isDefender:0,condition:{class:"TerrainCheck",terrainType:6}}]</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopOffsetInjurePerson", value:30, injury:1},{class:"TroopChangeDamage", value:20, isDefender:0}]</t>
+  </si>
+  <si>
+    <t>[{class:"TroopPreventPersonInjury"},{class:"TroopPreventPersonBattleDeath"},{class:"TroopChangeDamage", value:-20, isDefender:1}]</t>
   </si>
 </sst>
 </file>
@@ -3033,7 +3039,9 @@
       <c r="H56" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I56" s="24"/>
+      <c r="I56" s="24" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B57" s="25">
@@ -3056,6 +3064,9 @@
       </c>
       <c r="H57" s="25" t="s">
         <v>101</v>
+      </c>
+      <c r="I57" s="25" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
